--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-05 10:34</t>
+    <t xml:space="preserve">2026-08-16 09:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-16 09:46</t>
+    <t xml:space="preserve">2026-08-19 11:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">Serie</t>
   </si>
   <si>
-    <t xml:space="preserve">Region</t>
+    <t xml:space="preserve">Región</t>
   </si>
   <si>
     <t xml:space="preserve">Nacional</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-19 11:40</t>
+    <t xml:space="preserve">2026-08-28 11:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
+++ b/output/graficos_educacion_tasas/plot_regional_e_matricula_a_2018_los_rios_sexo.xlsx
@@ -64,7 +64,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-28 11:23</t>
+    <t xml:space="preserve">2026-09-06 17:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
